--- a/幻想少女公会招募图鉴.xlsx
+++ b/幻想少女公会招募图鉴.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$135</definedName>
     <definedName name="_xlnm.Criteria" localSheetId="0">Sheet1!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="798" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="167">
   <si>
     <t>位阶</t>
   </si>
@@ -54,18 +54,27 @@
     <t>传说</t>
   </si>
   <si>
+    <t>冰蛛女王</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>生灵</t>
+  </si>
+  <si>
+    <t>水系</t>
+  </si>
+  <si>
+    <t>雪原</t>
+  </si>
+  <si>
     <t>辰龙</t>
   </si>
   <si>
     <t>战士</t>
   </si>
   <si>
-    <t>生灵</t>
-  </si>
-  <si>
-    <t>水系</t>
-  </si>
-  <si>
     <t>沙滩</t>
   </si>
   <si>
@@ -90,9 +99,6 @@
     <t>风行游侠</t>
   </si>
   <si>
-    <t>射手</t>
-  </si>
-  <si>
     <t>风系</t>
   </si>
   <si>
@@ -186,7 +192,7 @@
     <t>雪人骑士</t>
   </si>
   <si>
-    <t>雪原</t>
+    <t>异界旅人</t>
   </si>
   <si>
     <t>鹰身公主</t>
@@ -201,6 +207,69 @@
     <t>亡灵</t>
   </si>
   <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>兵蜂猎手</t>
+  </si>
+  <si>
+    <t>兵蜂战士</t>
+  </si>
+  <si>
+    <t>沉默猎手</t>
+  </si>
+  <si>
+    <t>哥布林猎手</t>
+  </si>
+  <si>
+    <t>哥布林哨兵</t>
+  </si>
+  <si>
+    <t>荒漠盗贼</t>
+  </si>
+  <si>
+    <t>荒漠猎手</t>
+  </si>
+  <si>
+    <t>军团祭司</t>
+  </si>
+  <si>
+    <t>军团哨兵</t>
+  </si>
+  <si>
+    <t>矿洞采集者</t>
+  </si>
+  <si>
+    <t>矿洞淘金者</t>
+  </si>
+  <si>
+    <t>蓝灵菇娘</t>
+  </si>
+  <si>
+    <t>迷幻菇娘</t>
+  </si>
+  <si>
+    <t>史莱姆</t>
+  </si>
+  <si>
+    <t>史莱姆法师</t>
+  </si>
+  <si>
+    <t>史莱姆牧师</t>
+  </si>
+  <si>
+    <t>野猫猎手</t>
+  </si>
+  <si>
+    <t>鱼人祭司</t>
+  </si>
+  <si>
+    <t>鱼人哨兵</t>
+  </si>
+  <si>
+    <t>鱼人战士</t>
+  </si>
+  <si>
     <t>史诗</t>
   </si>
   <si>
@@ -463,69 +532,6 @@
   </si>
   <si>
     <t>游荡人偶</t>
-  </si>
-  <si>
-    <t>普通</t>
-  </si>
-  <si>
-    <t>兵蜂猎手</t>
-  </si>
-  <si>
-    <t>兵蜂战士</t>
-  </si>
-  <si>
-    <t>沉默猎手</t>
-  </si>
-  <si>
-    <t>哥布林猎手</t>
-  </si>
-  <si>
-    <t>哥布林哨兵</t>
-  </si>
-  <si>
-    <t>荒漠盗贼</t>
-  </si>
-  <si>
-    <t>荒漠猎手</t>
-  </si>
-  <si>
-    <t>军团祭司</t>
-  </si>
-  <si>
-    <t>军团哨兵</t>
-  </si>
-  <si>
-    <t>矿洞采集者</t>
-  </si>
-  <si>
-    <t>矿洞淘金者</t>
-  </si>
-  <si>
-    <t>蓝灵菇娘</t>
-  </si>
-  <si>
-    <t>迷幻菇娘</t>
-  </si>
-  <si>
-    <t>史莱姆</t>
-  </si>
-  <si>
-    <t>史莱姆法师</t>
-  </si>
-  <si>
-    <t>史莱姆牧师</t>
-  </si>
-  <si>
-    <t>野猫猎手</t>
-  </si>
-  <si>
-    <t>鱼人祭司</t>
-  </si>
-  <si>
-    <t>鱼人哨兵</t>
-  </si>
-  <si>
-    <t>鱼人战士</t>
   </si>
 </sst>
 </file>
@@ -1583,7 +1589,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F133"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr defaultColWidth="9.77777777777778" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="7.43518518518519" customWidth="1"/>
@@ -1616,19 +1622,19 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1636,20 +1642,20 @@
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1657,19 +1663,19 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1677,59 +1683,59 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>15</v>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>25</v>
+      <c r="E7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1737,39 +1743,39 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>15</v>
+      <c r="F9" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1777,39 +1783,39 @@
         <v>6</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="B11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1817,59 +1823,59 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>17</v>
+      <c r="E13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>36</v>
+      <c r="B14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1877,59 +1883,59 @@
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>36</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>36</v>
+      <c r="B17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1937,79 +1943,79 @@
         <v>6</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="B19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2017,19 +2023,19 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2040,56 +2046,56 @@
         <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>17</v>
+      <c r="C25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2100,1121 +2106,1121 @@
         <v>53</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>40</v>
+      <c r="D27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>15</v>
+        <v>6</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>15</v>
+      <c r="C29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>40</v>
+      <c r="F30" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>17</v>
+      <c r="C31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="2" t="s">
+      <c r="A32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>20</v>
+      <c r="C32" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="D33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="2" t="s">
+      <c r="A34" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="C34" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>15</v>
-      </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B35" s="2" t="s">
+      <c r="A35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>17</v>
+      <c r="C35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B36" s="2" t="s">
+      <c r="A36" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>36</v>
+      <c r="C36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>25</v>
+      <c r="D39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B41" s="5" t="s">
+      <c r="A41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>25</v>
+      <c r="C41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F42" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>36</v>
+      <c r="D45" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B46" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>36</v>
+      <c r="D46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" s="2" t="s">
+      <c r="A48" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>14</v>
+      <c r="C48" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F50" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C51" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>17</v>
+      <c r="D51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>17</v>
+        <v>79</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F53" s="5" t="s">
-        <v>25</v>
+      <c r="A53" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>15</v>
+        <v>79</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F58" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>30</v>
+        <v>9</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>36</v>
+        <v>79</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>11</v>
+        <v>79</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>40</v>
+        <v>79</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F63" s="2" t="s">
+      <c r="A63" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>17</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C66" s="3" t="s">
+      <c r="A66" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F66" s="3" t="s">
+      <c r="D66" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="5" t="s">
         <v>17</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>36</v>
+      <c r="F68" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>15</v>
+        <v>79</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E72" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F72" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>25</v>
+        <v>79</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E74" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F75" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B80" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>15</v>
+      <c r="C80" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>112</v>
@@ -3226,21 +3232,21 @@
         <v>9</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>9</v>
@@ -3249,12 +3255,12 @@
         <v>10</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>114</v>
@@ -3266,195 +3272,195 @@
         <v>9</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>117</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B88" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>17</v>
+      <c r="C88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B89" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E89" s="2" t="s">
+      <c r="C89" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B90" s="2" t="s">
+      <c r="A90" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B90" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>15</v>
+      <c r="C90" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>122</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B93" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>40</v>
+      <c r="C93" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>124</v>
@@ -3466,35 +3472,35 @@
         <v>9</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>126</v>
@@ -3503,704 +3509,704 @@
         <v>13</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>14</v>
+        <v>57</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B97" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>36</v>
+      <c r="C97" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E110" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F110" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B115" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C115" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>17</v>
+      <c r="C115" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="A116" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B116" s="3" t="s">
+      <c r="A116" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C116" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" s="3" t="s">
+      <c r="C116" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F116" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E117" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F117" s="2" t="s">
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" s="6" t="s">
+      <c r="F118" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F118" s="2" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="119" spans="1:6">
-      <c r="A119" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B119" s="3" t="s">
+      <c r="A119" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C119" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F119" s="3" t="s">
-        <v>25</v>
+      <c r="C119" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="120" spans="1:6">
-      <c r="A120" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B120" s="3" t="s">
+      <c r="A120" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C120" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>25</v>
+      <c r="C120" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B122" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C122" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F122" s="3" t="s">
+      <c r="C122" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E123" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B124" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C124" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>15</v>
+      <c r="C124" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="A127" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B127" s="6" t="s">
+      <c r="A127" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C127" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E127" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>36</v>
+      <c r="C127" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="129" spans="1:6">
-      <c r="A129" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B129" s="7" t="s">
+      <c r="A129" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C129" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E129" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F129" s="7" t="s">
-        <v>36</v>
+      <c r="C129" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>9</v>
@@ -4209,61 +4215,100 @@
         <v>10</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="132" spans="1:6">
-      <c r="A132" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B132" s="3" t="s">
+      <c r="A132" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C132" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>10</v>
+      <c r="C132" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B133" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="C133" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F133" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F133" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:F133">
-      <sortCondition ref="A2:A134" customList="传说,史诗,稀有,普通"/>
-      <sortCondition ref="B2:B134"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F135" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:F135">
+      <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <sortState ref="A2:F135">
     <sortCondition ref="A2:A135" customList="橙色,紫色,蓝色,绿色"/>
   </sortState>
-  <conditionalFormatting sqref="A2:F228">
+  <conditionalFormatting sqref="A2:F135 A145:F230">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A2="传说"</formula>
     </cfRule>

--- a/幻想少女公会招募图鉴.xlsx
+++ b/幻想少女公会招募图鉴.xlsx
@@ -249,7 +249,7 @@
     <t>迷幻菇娘</t>
   </si>
   <si>
-    <t>史莱姆</t>
+    <t>史莱姆战士</t>
   </si>
   <si>
     <t>史莱姆法师</t>
@@ -4300,7 +4300,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F135" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:F135">
+    <sortState ref="A1:F135">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>

--- a/幻想少女公会招募图鉴.xlsx
+++ b/幻想少女公会招募图鉴.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$136</definedName>
     <definedName name="_xlnm.Criteria" localSheetId="0">Sheet1!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="167">
   <si>
     <t>位阶</t>
   </si>
@@ -1589,13 +1589,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F135"/>
-  <sheetFormatPr defaultColWidth="9.77777777777778" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:F136"/>
+  <sheetFormatPr defaultColWidth="9.77477477477477" defaultRowHeight="13.25" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="7.43518518518519" customWidth="1"/>
-    <col min="2" max="2" width="12.3888888888889" customWidth="1"/>
-    <col min="3" max="3" width="9.31481481481481" customWidth="1"/>
-    <col min="4" max="6" width="9.77777777777778" customWidth="1"/>
+    <col min="1" max="1" width="7.43243243243243" customWidth="1"/>
+    <col min="2" max="2" width="12.3873873873874" customWidth="1"/>
+    <col min="3" max="3" width="9.31531531531532" customWidth="1"/>
+    <col min="4" max="6" width="9.77477477477477" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1638,7 +1638,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" ht="13.3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" ht="13.3" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" ht="13.3" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" ht="13.3" spans="1:6">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" ht="13.3" spans="1:6">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" ht="13.3" spans="1:6">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" ht="13.3" spans="1:6">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" ht="13.3" spans="1:6">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" ht="13.3" spans="1:6">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" ht="13.3" spans="1:6">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" ht="13.3" spans="1:6">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" ht="13.3" spans="1:6">
       <c r="A31" s="2" t="s">
         <v>58</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" ht="13.3" spans="1:6">
       <c r="A32" s="3" t="s">
         <v>58</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" ht="13.3" spans="1:6">
       <c r="A35" s="3" t="s">
         <v>58</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" ht="13.3" spans="1:6">
       <c r="A36" s="3" t="s">
         <v>58</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" ht="13.3" spans="1:6">
       <c r="A38" s="2" t="s">
         <v>58</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" ht="13.3" spans="1:6">
       <c r="A40" s="2" t="s">
         <v>58</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" ht="13.3" spans="1:6">
       <c r="A48" s="3" t="s">
         <v>58</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" ht="13.3" spans="1:6">
       <c r="A49" s="2" t="s">
         <v>58</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" ht="13.3" spans="1:6">
       <c r="A52" s="2" t="s">
         <v>79</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" ht="13.3" spans="1:6">
       <c r="A55" s="2" t="s">
         <v>79</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" ht="13.3" spans="1:6">
       <c r="A60" s="2" t="s">
         <v>79</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" ht="13.3" spans="1:6">
       <c r="A61" s="2" t="s">
         <v>79</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" ht="13.3" spans="1:6">
       <c r="A62" s="2" t="s">
         <v>79</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" ht="13.3" spans="1:6">
       <c r="A65" s="2" t="s">
         <v>79</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" ht="13.3" spans="1:6">
       <c r="A68" s="2" t="s">
         <v>79</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" ht="13.3" spans="1:6">
       <c r="A72" s="2" t="s">
         <v>79</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" ht="13.3" spans="1:6">
       <c r="A73" s="2" t="s">
         <v>79</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" ht="13.3" spans="1:6">
       <c r="A80" s="2" t="s">
         <v>79</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" ht="13.3" spans="1:6">
       <c r="A81" s="2" t="s">
         <v>79</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" ht="13.3" spans="1:6">
       <c r="A88" s="2" t="s">
         <v>79</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" ht="13.3" spans="1:6">
       <c r="A89" s="2" t="s">
         <v>79</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" ht="13.3" spans="1:6">
       <c r="A93" s="2" t="s">
         <v>79</v>
       </c>
@@ -3498,7 +3498,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" ht="13.3" spans="1:6">
       <c r="A96" s="2" t="s">
         <v>79</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" ht="13.3" spans="1:6">
       <c r="A97" s="2" t="s">
         <v>79</v>
       </c>
@@ -3563,10 +3563,10 @@
         <v>79</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>9</v>
@@ -3575,7 +3575,7 @@
         <v>26</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3583,7 +3583,7 @@
         <v>79</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>36</v>
@@ -3592,7 +3592,7 @@
         <v>9</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>20</v>
@@ -3603,7 +3603,7 @@
         <v>79</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>36</v>
@@ -3612,30 +3612,30 @@
         <v>9</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="2" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3643,16 +3643,16 @@
         <v>132</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>18</v>
@@ -3663,16 +3663,16 @@
         <v>132</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>18</v>
@@ -3683,19 +3683,19 @@
         <v>132</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3703,19 +3703,19 @@
         <v>132</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3723,19 +3723,19 @@
         <v>132</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3743,10 +3743,10 @@
         <v>132</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>9</v>
@@ -3763,7 +3763,7 @@
         <v>132</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>13</v>
@@ -3772,10 +3772,10 @@
         <v>9</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3783,7 +3783,7 @@
         <v>132</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>13</v>
@@ -3795,7 +3795,7 @@
         <v>32</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3803,7 +3803,7 @@
         <v>132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>13</v>
@@ -3812,7 +3812,7 @@
         <v>9</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>20</v>
@@ -3823,7 +3823,7 @@
         <v>132</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>13</v>
@@ -3835,7 +3835,7 @@
         <v>17</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3843,10 +3843,10 @@
         <v>132</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>9</v>
@@ -3863,7 +3863,7 @@
         <v>132</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>8</v>
@@ -3872,10 +3872,10 @@
         <v>9</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3883,19 +3883,19 @@
         <v>132</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3903,7 +3903,7 @@
         <v>132</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>13</v>
@@ -3912,10 +3912,10 @@
         <v>9</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3923,10 +3923,10 @@
         <v>132</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>9</v>
@@ -3943,16 +3943,16 @@
         <v>132</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>20</v>
@@ -3963,19 +3963,19 @@
         <v>132</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3983,19 +3983,19 @@
         <v>132</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -4003,19 +4003,19 @@
         <v>132</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4023,16 +4023,16 @@
         <v>132</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>38</v>
@@ -4043,7 +4043,7 @@
         <v>132</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>13</v>
@@ -4052,10 +4052,10 @@
         <v>9</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -4063,7 +4063,7 @@
         <v>132</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>13</v>
@@ -4072,10 +4072,10 @@
         <v>9</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -4083,19 +4083,19 @@
         <v>132</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -4103,19 +4103,19 @@
         <v>132</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4123,16 +4123,16 @@
         <v>132</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>38</v>
@@ -4143,16 +4143,16 @@
         <v>132</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>38</v>
@@ -4163,19 +4163,19 @@
         <v>132</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4183,19 +4183,19 @@
         <v>132</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4203,10 +4203,10 @@
         <v>132</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>9</v>
@@ -4223,7 +4223,7 @@
         <v>132</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>13</v>
@@ -4232,10 +4232,10 @@
         <v>9</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4243,19 +4243,19 @@
         <v>132</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4263,10 +4263,10 @@
         <v>132</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>57</v>
@@ -4283,24 +4283,44 @@
         <v>132</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F135" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F136" s="2" t="s">
         <v>18</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F135" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:F135">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F136" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:F136">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -4308,7 +4328,7 @@
   <sortState ref="A2:F135">
     <sortCondition ref="A2:A135" customList="橙色,紫色,蓝色,绿色"/>
   </sortState>
-  <conditionalFormatting sqref="A2:F135 A145:F230">
+  <conditionalFormatting sqref="A2:F136 A146:F231">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A2="传说"</formula>
     </cfRule>
